--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N83_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N83_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>60.46687683954959</v>
+        <v>9.825867486426809</v>
       </c>
       <c r="D2" t="n">
-        <v>56.44791613465274</v>
+        <v>9.17278637188107</v>
       </c>
       <c r="E2" t="n">
-        <v>5.913845074080628</v>
+        <v>0.9609998245381018</v>
       </c>
       <c r="F2" t="n">
-        <v>14.63549330380093</v>
+        <v>2.378267661867651</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>47.54366409208377</v>
+        <v>7.725845414963612</v>
       </c>
       <c r="D3" t="n">
-        <v>37.65083076691607</v>
+        <v>6.118259999623861</v>
       </c>
       <c r="E3" t="n">
-        <v>5.913845074080628</v>
+        <v>0.9609998245381018</v>
       </c>
       <c r="F3" t="n">
-        <v>14.63549330380093</v>
+        <v>2.378267661867651</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.33613873462301</v>
+        <v>7.52962254437624</v>
       </c>
       <c r="D4" t="n">
-        <v>16.03097789119827</v>
+        <v>2.605033907319719</v>
       </c>
       <c r="E4" t="n">
-        <v>5.913845074080628</v>
+        <v>0.9609998245381018</v>
       </c>
       <c r="F4" t="n">
-        <v>14.63549330380093</v>
+        <v>2.378267661867651</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.23486615823657</v>
+        <v>9.138165750713442</v>
       </c>
       <c r="D5" t="n">
-        <v>43.89305574158359</v>
+        <v>7.132621558007334</v>
       </c>
       <c r="E5" t="n">
-        <v>5.913845074080628</v>
+        <v>0.9609998245381018</v>
       </c>
       <c r="F5" t="n">
-        <v>14.63549330380093</v>
+        <v>2.378267661867651</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
